--- a/tools/importer/reports/import-screening-detail-page.report.xlsx
+++ b/tools/importer/reports/import-screening-detail-page.report.xlsx
@@ -52,7 +52,7 @@
     <t>screening-detail-page</t>
   </si>
   <si>
-    <t>2026-06-17T19:12:28.352Z</t>
+    <t>2026-06-17T20:20:36.973Z</t>
   </si>
   <si>
     <t>Mammograms &amp; Breast Cancer Screening | UT MD Anderson</t>
